--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -6885,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120900790</v>
+        <v>120900759</v>
       </c>
       <c r="B60" t="n">
-        <v>91957</v>
+        <v>91975</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6897,25 +6897,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>756482</v>
+        <v>756485</v>
       </c>
       <c r="R60" t="n">
-        <v>7458190</v>
+        <v>7458182</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120900759</v>
+        <v>120900790</v>
       </c>
       <c r="B61" t="n">
-        <v>91975</v>
+        <v>91957</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7003,25 +7003,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>756485</v>
+        <v>756482</v>
       </c>
       <c r="R61" t="n">
-        <v>7458182</v>
+        <v>7458190</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -5719,10 +5719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120900764</v>
+        <v>120900773</v>
       </c>
       <c r="B49" t="n">
-        <v>91955</v>
+        <v>89358</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>756511</v>
+        <v>756191</v>
       </c>
       <c r="R49" t="n">
-        <v>7458174</v>
+        <v>7458245</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120900782</v>
+        <v>120900768</v>
       </c>
       <c r="B50" t="n">
-        <v>89370</v>
+        <v>91965</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5837,25 +5837,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>756009</v>
+        <v>756127</v>
       </c>
       <c r="R50" t="n">
-        <v>7458239</v>
+        <v>7458227</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120900783</v>
+        <v>120900751</v>
       </c>
       <c r="B51" t="n">
-        <v>89370</v>
+        <v>91599</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5943,25 +5943,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>756063</v>
+        <v>756155</v>
       </c>
       <c r="R51" t="n">
         <v>7458252</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120900766</v>
+        <v>120900775</v>
       </c>
       <c r="B52" t="n">
-        <v>91955</v>
+        <v>89358</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6049,25 +6049,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6077,10 +6077,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>756045</v>
+        <v>756214</v>
       </c>
       <c r="R52" t="n">
-        <v>7458254</v>
+        <v>7458231</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120900775</v>
+        <v>120900772</v>
       </c>
       <c r="B53" t="n">
-        <v>89348</v>
+        <v>89358</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>756214</v>
+        <v>756115</v>
       </c>
       <c r="R53" t="n">
-        <v>7458231</v>
+        <v>7458239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120900802</v>
+        <v>120900790</v>
       </c>
       <c r="B54" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>756093</v>
+        <v>756482</v>
       </c>
       <c r="R54" t="n">
-        <v>7458237</v>
+        <v>7458190</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120900750</v>
+        <v>120900795</v>
       </c>
       <c r="B55" t="n">
-        <v>91589</v>
+        <v>91967</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6371,21 +6371,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>756008</v>
+        <v>756180</v>
       </c>
       <c r="R55" t="n">
-        <v>7458255</v>
+        <v>7458154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120900768</v>
+        <v>120900803</v>
       </c>
       <c r="B56" t="n">
-        <v>91955</v>
+        <v>91967</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6477,21 +6477,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>756127</v>
+        <v>756131</v>
       </c>
       <c r="R56" t="n">
-        <v>7458227</v>
+        <v>7458241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120900767</v>
+        <v>120900764</v>
       </c>
       <c r="B57" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>756054</v>
+        <v>756511</v>
       </c>
       <c r="R57" t="n">
-        <v>7458249</v>
+        <v>7458174</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120900745</v>
+        <v>120900782</v>
       </c>
       <c r="B58" t="n">
-        <v>91988</v>
+        <v>89380</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6685,25 +6685,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>756479</v>
+        <v>756009</v>
       </c>
       <c r="R58" t="n">
-        <v>7458192</v>
+        <v>7458239</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120900765</v>
+        <v>120900759</v>
       </c>
       <c r="B59" t="n">
-        <v>91955</v>
+        <v>91985</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6791,25 +6791,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>756236</v>
+        <v>756485</v>
       </c>
       <c r="R59" t="n">
-        <v>7458187</v>
+        <v>7458182</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120900759</v>
+        <v>120900794</v>
       </c>
       <c r="B60" t="n">
-        <v>91975</v>
+        <v>91967</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6897,25 +6897,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>756485</v>
+        <v>756199</v>
       </c>
       <c r="R60" t="n">
-        <v>7458182</v>
+        <v>7458178</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120900790</v>
+        <v>120900769</v>
       </c>
       <c r="B61" t="n">
-        <v>91957</v>
+        <v>91965</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>756482</v>
+        <v>756193</v>
       </c>
       <c r="R61" t="n">
-        <v>7458190</v>
+        <v>7458248</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,10 +7097,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120900795</v>
+        <v>120900745</v>
       </c>
       <c r="B62" t="n">
-        <v>91957</v>
+        <v>91998</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>756180</v>
+        <v>756479</v>
       </c>
       <c r="R62" t="n">
-        <v>7458154</v>
+        <v>7458192</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120900773</v>
+        <v>120900789</v>
       </c>
       <c r="B63" t="n">
-        <v>89348</v>
+        <v>91967</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7215,25 +7215,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>756191</v>
+        <v>756556</v>
       </c>
       <c r="R63" t="n">
-        <v>7458245</v>
+        <v>7458181</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120900800</v>
+        <v>120900801</v>
       </c>
       <c r="B64" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>756038</v>
+        <v>756049</v>
       </c>
       <c r="R64" t="n">
-        <v>7458259</v>
+        <v>7458248</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120900751</v>
+        <v>120900767</v>
       </c>
       <c r="B65" t="n">
-        <v>91589</v>
+        <v>91965</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>756155</v>
+        <v>756054</v>
       </c>
       <c r="R65" t="n">
-        <v>7458252</v>
+        <v>7458249</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7521,10 +7521,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120900769</v>
+        <v>120900784</v>
       </c>
       <c r="B66" t="n">
-        <v>91955</v>
+        <v>89380</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7533,25 +7533,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>756193</v>
+        <v>756086</v>
       </c>
       <c r="R66" t="n">
-        <v>7458248</v>
+        <v>7458254</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120900774</v>
+        <v>120900805</v>
       </c>
       <c r="B67" t="n">
-        <v>89348</v>
+        <v>91967</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7639,25 +7639,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>756195</v>
+        <v>756219</v>
       </c>
       <c r="R67" t="n">
-        <v>7458248</v>
+        <v>7458235</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120900794</v>
+        <v>120900766</v>
       </c>
       <c r="B68" t="n">
-        <v>91957</v>
+        <v>91965</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>756199</v>
+        <v>756045</v>
       </c>
       <c r="R68" t="n">
-        <v>7458178</v>
+        <v>7458254</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7839,10 +7839,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120900805</v>
+        <v>120900802</v>
       </c>
       <c r="B69" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>756219</v>
+        <v>756093</v>
       </c>
       <c r="R69" t="n">
-        <v>7458235</v>
+        <v>7458237</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7948,7 +7948,7 @@
         <v>120900799</v>
       </c>
       <c r="B70" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120900803</v>
+        <v>120900800</v>
       </c>
       <c r="B71" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>756131</v>
+        <v>756038</v>
       </c>
       <c r="R71" t="n">
-        <v>7458241</v>
+        <v>7458259</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8157,10 +8157,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120900772</v>
+        <v>120900774</v>
       </c>
       <c r="B72" t="n">
-        <v>89348</v>
+        <v>89358</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8197,10 +8197,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>756115</v>
+        <v>756195</v>
       </c>
       <c r="R72" t="n">
-        <v>7458239</v>
+        <v>7458248</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120900747</v>
+        <v>120900750</v>
       </c>
       <c r="B73" t="n">
-        <v>91988</v>
+        <v>91599</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3100</v>
+        <v>4745</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>756139</v>
+        <v>756008</v>
       </c>
       <c r="R73" t="n">
-        <v>7458245</v>
+        <v>7458255</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8372,7 +8372,7 @@
         <v>120900804</v>
       </c>
       <c r="B74" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8475,10 +8475,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120900784</v>
+        <v>120900747</v>
       </c>
       <c r="B75" t="n">
-        <v>89370</v>
+        <v>91998</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8487,25 +8487,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>756086</v>
+        <v>756139</v>
       </c>
       <c r="R75" t="n">
-        <v>7458254</v>
+        <v>7458245</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8581,10 +8581,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120900801</v>
+        <v>120900765</v>
       </c>
       <c r="B76" t="n">
-        <v>91957</v>
+        <v>91965</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8597,21 +8597,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>756049</v>
+        <v>756236</v>
       </c>
       <c r="R76" t="n">
-        <v>7458248</v>
+        <v>7458187</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8687,10 +8687,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120900789</v>
+        <v>120900783</v>
       </c>
       <c r="B77" t="n">
-        <v>91957</v>
+        <v>89380</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8699,25 +8699,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8727,10 +8727,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>756556</v>
+        <v>756063</v>
       </c>
       <c r="R77" t="n">
-        <v>7458181</v>
+        <v>7458252</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121150821</v>
+        <v>121150824</v>
       </c>
       <c r="B78" t="n">
-        <v>91955</v>
+        <v>91967</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8809,26 +8809,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756127</v>
+        <v>756060</v>
       </c>
       <c r="R78" t="n">
-        <v>7458223</v>
+        <v>7458231</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121150824</v>
+        <v>121150825</v>
       </c>
       <c r="B79" t="n">
-        <v>91957</v>
+        <v>89380</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8916,30 +8916,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756060</v>
+        <v>756175</v>
       </c>
       <c r="R79" t="n">
-        <v>7458231</v>
+        <v>7458176</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121152431</v>
+        <v>121150822</v>
       </c>
       <c r="B80" t="n">
-        <v>91947</v>
+        <v>91967</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9027,25 +9027,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756226</v>
+        <v>756502</v>
       </c>
       <c r="R80" t="n">
-        <v>7458150</v>
+        <v>7458196</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121150825</v>
+        <v>121150821</v>
       </c>
       <c r="B81" t="n">
-        <v>89370</v>
+        <v>91965</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9138,25 +9138,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>756175</v>
+        <v>756127</v>
       </c>
       <c r="R81" t="n">
-        <v>7458176</v>
+        <v>7458223</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9237,7 +9237,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121150822</v>
+        <v>121152430</v>
       </c>
       <c r="B82" t="n">
         <v>91957</v>
@@ -9249,25 +9249,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756502</v>
+        <v>756201</v>
       </c>
       <c r="R82" t="n">
-        <v>7458196</v>
+        <v>7458210</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9348,10 +9348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121150826</v>
+        <v>121150823</v>
       </c>
       <c r="B83" t="n">
-        <v>91957</v>
+        <v>91999</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>756199</v>
+        <v>756349</v>
       </c>
       <c r="R83" t="n">
-        <v>7458177</v>
+        <v>7458017</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121150827</v>
+        <v>121150826</v>
       </c>
       <c r="B84" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756515</v>
+        <v>756199</v>
       </c>
       <c r="R84" t="n">
         <v>7458177</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121152430</v>
+        <v>121150827</v>
       </c>
       <c r="B85" t="n">
-        <v>91947</v>
+        <v>91967</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756201</v>
+        <v>756515</v>
       </c>
       <c r="R85" t="n">
-        <v>7458210</v>
+        <v>7458177</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121150823</v>
+        <v>121152431</v>
       </c>
       <c r="B86" t="n">
-        <v>91989</v>
+        <v>91957</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9693,25 +9693,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5448</v>
+        <v>6055</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756349</v>
+        <v>756226</v>
       </c>
       <c r="R86" t="n">
-        <v>7458017</v>
+        <v>7458150</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -5719,10 +5719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120900773</v>
+        <v>120900747</v>
       </c>
       <c r="B49" t="n">
-        <v>89358</v>
+        <v>91998</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>756191</v>
+        <v>756139</v>
       </c>
       <c r="R49" t="n">
         <v>7458245</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120900768</v>
+        <v>120900745</v>
       </c>
       <c r="B50" t="n">
-        <v>91965</v>
+        <v>91998</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>756127</v>
+        <v>756479</v>
       </c>
       <c r="R50" t="n">
-        <v>7458227</v>
+        <v>7458192</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120900751</v>
+        <v>120900764</v>
       </c>
       <c r="B51" t="n">
-        <v>91599</v>
+        <v>91965</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5947,21 +5947,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>756155</v>
+        <v>756511</v>
       </c>
       <c r="R51" t="n">
-        <v>7458252</v>
+        <v>7458174</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6037,7 +6037,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120900775</v>
+        <v>120900772</v>
       </c>
       <c r="B52" t="n">
         <v>89358</v>
@@ -6077,10 +6077,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>756214</v>
+        <v>756115</v>
       </c>
       <c r="R52" t="n">
-        <v>7458231</v>
+        <v>7458239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120900772</v>
+        <v>120900773</v>
       </c>
       <c r="B53" t="n">
         <v>89358</v>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>756115</v>
+        <v>756191</v>
       </c>
       <c r="R53" t="n">
-        <v>7458239</v>
+        <v>7458245</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120900790</v>
+        <v>120900768</v>
       </c>
       <c r="B54" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6265,21 +6265,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>756482</v>
+        <v>756127</v>
       </c>
       <c r="R54" t="n">
-        <v>7458190</v>
+        <v>7458227</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120900795</v>
+        <v>120900765</v>
       </c>
       <c r="B55" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6371,21 +6371,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6395,10 +6395,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>756180</v>
+        <v>756236</v>
       </c>
       <c r="R55" t="n">
-        <v>7458154</v>
+        <v>7458187</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120900803</v>
+        <v>120900801</v>
       </c>
       <c r="B56" t="n">
         <v>91967</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>756131</v>
+        <v>756049</v>
       </c>
       <c r="R56" t="n">
-        <v>7458241</v>
+        <v>7458248</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6567,10 +6567,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120900764</v>
+        <v>120900803</v>
       </c>
       <c r="B57" t="n">
-        <v>91965</v>
+        <v>91967</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6583,21 +6583,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>756511</v>
+        <v>756131</v>
       </c>
       <c r="R57" t="n">
-        <v>7458174</v>
+        <v>7458241</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120900782</v>
+        <v>120900805</v>
       </c>
       <c r="B58" t="n">
-        <v>89380</v>
+        <v>91967</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6685,25 +6685,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>756009</v>
+        <v>756219</v>
       </c>
       <c r="R58" t="n">
-        <v>7458239</v>
+        <v>7458235</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120900759</v>
+        <v>120900775</v>
       </c>
       <c r="B59" t="n">
-        <v>91985</v>
+        <v>89358</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6791,25 +6791,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>756485</v>
+        <v>756214</v>
       </c>
       <c r="R59" t="n">
-        <v>7458182</v>
+        <v>7458231</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120900794</v>
+        <v>120900767</v>
       </c>
       <c r="B60" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6901,21 +6901,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>756199</v>
+        <v>756054</v>
       </c>
       <c r="R60" t="n">
-        <v>7458178</v>
+        <v>7458249</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120900769</v>
+        <v>120900751</v>
       </c>
       <c r="B61" t="n">
-        <v>91965</v>
+        <v>91599</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>756193</v>
+        <v>756155</v>
       </c>
       <c r="R61" t="n">
-        <v>7458248</v>
+        <v>7458252</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,10 +7097,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120900745</v>
+        <v>120900794</v>
       </c>
       <c r="B62" t="n">
-        <v>91998</v>
+        <v>91967</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>756479</v>
+        <v>756199</v>
       </c>
       <c r="R62" t="n">
-        <v>7458192</v>
+        <v>7458178</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120900789</v>
+        <v>120900766</v>
       </c>
       <c r="B63" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7219,21 +7219,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>756556</v>
+        <v>756045</v>
       </c>
       <c r="R63" t="n">
-        <v>7458181</v>
+        <v>7458254</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120900801</v>
+        <v>120900782</v>
       </c>
       <c r="B64" t="n">
-        <v>91967</v>
+        <v>89380</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7321,25 +7321,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>756049</v>
+        <v>756009</v>
       </c>
       <c r="R64" t="n">
-        <v>7458248</v>
+        <v>7458239</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120900767</v>
+        <v>120900784</v>
       </c>
       <c r="B65" t="n">
-        <v>91965</v>
+        <v>89380</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7427,25 +7427,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>756054</v>
+        <v>756086</v>
       </c>
       <c r="R65" t="n">
-        <v>7458249</v>
+        <v>7458254</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7521,10 +7521,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120900784</v>
+        <v>120900802</v>
       </c>
       <c r="B66" t="n">
-        <v>89380</v>
+        <v>91967</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7533,25 +7533,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>756086</v>
+        <v>756093</v>
       </c>
       <c r="R66" t="n">
-        <v>7458254</v>
+        <v>7458237</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7627,7 +7627,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120900805</v>
+        <v>120900800</v>
       </c>
       <c r="B67" t="n">
         <v>91967</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>756219</v>
+        <v>756038</v>
       </c>
       <c r="R67" t="n">
-        <v>7458235</v>
+        <v>7458259</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120900766</v>
+        <v>120900774</v>
       </c>
       <c r="B68" t="n">
-        <v>91965</v>
+        <v>89358</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7745,25 +7745,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>756045</v>
+        <v>756195</v>
       </c>
       <c r="R68" t="n">
-        <v>7458254</v>
+        <v>7458248</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7839,10 +7839,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120900802</v>
+        <v>120900750</v>
       </c>
       <c r="B69" t="n">
-        <v>91967</v>
+        <v>91599</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7855,21 +7855,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>756093</v>
+        <v>756008</v>
       </c>
       <c r="R69" t="n">
-        <v>7458237</v>
+        <v>7458255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120900799</v>
+        <v>120900790</v>
       </c>
       <c r="B70" t="n">
         <v>91967</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>755998</v>
+        <v>756482</v>
       </c>
       <c r="R70" t="n">
-        <v>7458251</v>
+        <v>7458190</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8051,7 +8051,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120900800</v>
+        <v>120900799</v>
       </c>
       <c r="B71" t="n">
         <v>91967</v>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>756038</v>
+        <v>755998</v>
       </c>
       <c r="R71" t="n">
-        <v>7458259</v>
+        <v>7458251</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8157,10 +8157,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120900774</v>
+        <v>120900804</v>
       </c>
       <c r="B72" t="n">
-        <v>89358</v>
+        <v>91967</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8169,25 +8169,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8197,10 +8197,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>756195</v>
+        <v>756179</v>
       </c>
       <c r="R72" t="n">
-        <v>7458248</v>
+        <v>7458258</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120900750</v>
+        <v>120900789</v>
       </c>
       <c r="B73" t="n">
-        <v>91599</v>
+        <v>91967</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>756008</v>
+        <v>756556</v>
       </c>
       <c r="R73" t="n">
-        <v>7458255</v>
+        <v>7458181</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8369,10 +8369,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120900804</v>
+        <v>120900769</v>
       </c>
       <c r="B74" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>756179</v>
+        <v>756193</v>
       </c>
       <c r="R74" t="n">
-        <v>7458258</v>
+        <v>7458248</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8475,10 +8475,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120900747</v>
+        <v>120900759</v>
       </c>
       <c r="B75" t="n">
-        <v>91998</v>
+        <v>91985</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8487,25 +8487,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>756139</v>
+        <v>756485</v>
       </c>
       <c r="R75" t="n">
-        <v>7458245</v>
+        <v>7458182</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8581,10 +8581,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120900765</v>
+        <v>120900795</v>
       </c>
       <c r="B76" t="n">
-        <v>91965</v>
+        <v>91967</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8597,21 +8597,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>756236</v>
+        <v>756180</v>
       </c>
       <c r="R76" t="n">
-        <v>7458187</v>
+        <v>7458154</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121150824</v>
+        <v>121150823</v>
       </c>
       <c r="B78" t="n">
-        <v>91967</v>
+        <v>91999</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8809,26 +8809,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756060</v>
+        <v>756349</v>
       </c>
       <c r="R78" t="n">
-        <v>7458231</v>
+        <v>7458017</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121150822</v>
+        <v>121150821</v>
       </c>
       <c r="B80" t="n">
-        <v>91967</v>
+        <v>91965</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9031,21 +9031,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756502</v>
+        <v>756127</v>
       </c>
       <c r="R80" t="n">
-        <v>7458196</v>
+        <v>7458223</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121150821</v>
+        <v>121150826</v>
       </c>
       <c r="B81" t="n">
-        <v>91965</v>
+        <v>91967</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9142,21 +9142,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>756127</v>
+        <v>756199</v>
       </c>
       <c r="R81" t="n">
-        <v>7458223</v>
+        <v>7458177</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9237,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121152430</v>
+        <v>121150824</v>
       </c>
       <c r="B82" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,30 +9249,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756201</v>
+        <v>756060</v>
       </c>
       <c r="R82" t="n">
-        <v>7458210</v>
+        <v>7458231</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9348,10 +9348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121150823</v>
+        <v>121150822</v>
       </c>
       <c r="B83" t="n">
-        <v>91999</v>
+        <v>91967</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>756349</v>
+        <v>756502</v>
       </c>
       <c r="R83" t="n">
-        <v>7458017</v>
+        <v>7458196</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121150826</v>
+        <v>121152430</v>
       </c>
       <c r="B84" t="n">
-        <v>91967</v>
+        <v>91957</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9471,25 +9471,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756199</v>
+        <v>756201</v>
       </c>
       <c r="R84" t="n">
-        <v>7458177</v>
+        <v>7458210</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9533,12 +9533,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121150827</v>
+        <v>121152431</v>
       </c>
       <c r="B85" t="n">
-        <v>91967</v>
+        <v>91957</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756515</v>
+        <v>756226</v>
       </c>
       <c r="R85" t="n">
-        <v>7458177</v>
+        <v>7458150</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121152431</v>
+        <v>121150827</v>
       </c>
       <c r="B86" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9693,25 +9693,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756226</v>
+        <v>756515</v>
       </c>
       <c r="R86" t="n">
-        <v>7458150</v>
+        <v>7458177</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -6673,10 +6673,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120900805</v>
+        <v>120900775</v>
       </c>
       <c r="B58" t="n">
-        <v>91967</v>
+        <v>89358</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6685,25 +6685,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>756219</v>
+        <v>756214</v>
       </c>
       <c r="R58" t="n">
-        <v>7458235</v>
+        <v>7458231</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120900775</v>
+        <v>120900805</v>
       </c>
       <c r="B59" t="n">
-        <v>89358</v>
+        <v>91967</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6791,25 +6791,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>756214</v>
+        <v>756219</v>
       </c>
       <c r="R59" t="n">
-        <v>7458231</v>
+        <v>7458235</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121150823</v>
+        <v>121150826</v>
       </c>
       <c r="B78" t="n">
-        <v>91999</v>
+        <v>91979</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756349</v>
+        <v>756199</v>
       </c>
       <c r="R78" t="n">
-        <v>7458017</v>
+        <v>7458177</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121150825</v>
+        <v>121150824</v>
       </c>
       <c r="B79" t="n">
-        <v>89380</v>
+        <v>91979</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8916,30 +8916,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756175</v>
+        <v>756060</v>
       </c>
       <c r="R79" t="n">
-        <v>7458176</v>
+        <v>7458231</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121150821</v>
+        <v>121150827</v>
       </c>
       <c r="B80" t="n">
-        <v>91965</v>
+        <v>91979</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9031,21 +9031,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756127</v>
+        <v>756515</v>
       </c>
       <c r="R80" t="n">
-        <v>7458223</v>
+        <v>7458177</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121150826</v>
+        <v>121150822</v>
       </c>
       <c r="B81" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>756199</v>
+        <v>756502</v>
       </c>
       <c r="R81" t="n">
-        <v>7458177</v>
+        <v>7458196</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9237,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121150824</v>
+        <v>121150823</v>
       </c>
       <c r="B82" t="n">
-        <v>91967</v>
+        <v>92011</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9253,26 +9253,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756060</v>
+        <v>756349</v>
       </c>
       <c r="R82" t="n">
-        <v>7458231</v>
+        <v>7458017</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9348,10 +9348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121150822</v>
+        <v>121150825</v>
       </c>
       <c r="B83" t="n">
-        <v>91967</v>
+        <v>89387</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9360,25 +9360,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>756502</v>
+        <v>756175</v>
       </c>
       <c r="R83" t="n">
-        <v>7458196</v>
+        <v>7458176</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121152430</v>
+        <v>121152431</v>
       </c>
       <c r="B84" t="n">
-        <v>91957</v>
+        <v>91969</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756201</v>
+        <v>756226</v>
       </c>
       <c r="R84" t="n">
-        <v>7458210</v>
+        <v>7458150</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121152431</v>
+        <v>121152430</v>
       </c>
       <c r="B85" t="n">
-        <v>91957</v>
+        <v>91969</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756226</v>
+        <v>756201</v>
       </c>
       <c r="R85" t="n">
-        <v>7458150</v>
+        <v>7458210</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121150827</v>
+        <v>121150821</v>
       </c>
       <c r="B86" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756515</v>
+        <v>756127</v>
       </c>
       <c r="R86" t="n">
-        <v>7458177</v>
+        <v>7458223</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121150826</v>
+        <v>121152431</v>
       </c>
       <c r="B78" t="n">
-        <v>91979</v>
+        <v>91970</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8805,25 +8805,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756199</v>
+        <v>756226</v>
       </c>
       <c r="R78" t="n">
-        <v>7458177</v>
+        <v>7458150</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121150824</v>
+        <v>121150826</v>
       </c>
       <c r="B79" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756060</v>
+        <v>756199</v>
       </c>
       <c r="R79" t="n">
-        <v>7458231</v>
+        <v>7458177</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9015,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121150827</v>
+        <v>121150824</v>
       </c>
       <c r="B80" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756515</v>
+        <v>756060</v>
       </c>
       <c r="R80" t="n">
-        <v>7458177</v>
+        <v>7458231</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9129,7 +9129,7 @@
         <v>121150822</v>
       </c>
       <c r="B81" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121150823</v>
+        <v>121152430</v>
       </c>
       <c r="B82" t="n">
-        <v>92011</v>
+        <v>91970</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,25 +9249,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5448</v>
+        <v>6055</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756349</v>
+        <v>756201</v>
       </c>
       <c r="R82" t="n">
-        <v>7458017</v>
+        <v>7458210</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9351,7 +9351,7 @@
         <v>121150825</v>
       </c>
       <c r="B83" t="n">
-        <v>89387</v>
+        <v>89388</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121152431</v>
+        <v>121150827</v>
       </c>
       <c r="B84" t="n">
-        <v>91969</v>
+        <v>91980</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9471,25 +9471,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756226</v>
+        <v>756515</v>
       </c>
       <c r="R84" t="n">
-        <v>7458150</v>
+        <v>7458177</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9533,12 +9533,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121152430</v>
+        <v>121150821</v>
       </c>
       <c r="B85" t="n">
-        <v>91969</v>
+        <v>91978</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756201</v>
+        <v>756127</v>
       </c>
       <c r="R85" t="n">
-        <v>7458210</v>
+        <v>7458223</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121150821</v>
+        <v>121150823</v>
       </c>
       <c r="B86" t="n">
-        <v>91977</v>
+        <v>92012</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756127</v>
+        <v>756349</v>
       </c>
       <c r="R86" t="n">
-        <v>7458223</v>
+        <v>7458017</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121152431</v>
+        <v>121150824</v>
       </c>
       <c r="B78" t="n">
-        <v>91970</v>
+        <v>91983</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8805,30 +8805,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756226</v>
+        <v>756060</v>
       </c>
       <c r="R78" t="n">
-        <v>7458150</v>
+        <v>7458231</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121150826</v>
+        <v>121150822</v>
       </c>
       <c r="B79" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756199</v>
+        <v>756502</v>
       </c>
       <c r="R79" t="n">
-        <v>7458177</v>
+        <v>7458196</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9015,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121150824</v>
+        <v>121150827</v>
       </c>
       <c r="B80" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756060</v>
+        <v>756515</v>
       </c>
       <c r="R80" t="n">
-        <v>7458231</v>
+        <v>7458177</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121150822</v>
+        <v>121150825</v>
       </c>
       <c r="B81" t="n">
-        <v>91980</v>
+        <v>89391</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9138,25 +9138,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>756502</v>
+        <v>756175</v>
       </c>
       <c r="R81" t="n">
-        <v>7458196</v>
+        <v>7458176</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9237,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121152430</v>
+        <v>121150821</v>
       </c>
       <c r="B82" t="n">
-        <v>91970</v>
+        <v>91981</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,25 +9249,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756201</v>
+        <v>756127</v>
       </c>
       <c r="R82" t="n">
-        <v>7458210</v>
+        <v>7458223</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9348,10 +9348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121150825</v>
+        <v>121152431</v>
       </c>
       <c r="B83" t="n">
-        <v>89388</v>
+        <v>91973</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>756175</v>
+        <v>756226</v>
       </c>
       <c r="R83" t="n">
-        <v>7458176</v>
+        <v>7458150</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9459,10 +9459,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121150827</v>
+        <v>121150826</v>
       </c>
       <c r="B84" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756515</v>
+        <v>756199</v>
       </c>
       <c r="R84" t="n">
         <v>7458177</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121150821</v>
+        <v>121150823</v>
       </c>
       <c r="B85" t="n">
-        <v>91978</v>
+        <v>92015</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9586,21 +9586,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756127</v>
+        <v>756349</v>
       </c>
       <c r="R85" t="n">
-        <v>7458223</v>
+        <v>7458017</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121150823</v>
+        <v>121152430</v>
       </c>
       <c r="B86" t="n">
-        <v>92012</v>
+        <v>91973</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9693,25 +9693,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5448</v>
+        <v>6055</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756349</v>
+        <v>756201</v>
       </c>
       <c r="R86" t="n">
-        <v>7458017</v>
+        <v>7458210</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121150822</v>
+        <v>121152430</v>
       </c>
       <c r="B79" t="n">
-        <v>91983</v>
+        <v>91973</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8916,25 +8916,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756502</v>
+        <v>756201</v>
       </c>
       <c r="R79" t="n">
-        <v>7458196</v>
+        <v>7458210</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9015,7 +9015,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121150827</v>
+        <v>121150822</v>
       </c>
       <c r="B80" t="n">
         <v>91983</v>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>756515</v>
+        <v>756502</v>
       </c>
       <c r="R80" t="n">
-        <v>7458177</v>
+        <v>7458196</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9089,12 +9089,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9126,10 +9126,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121150825</v>
+        <v>121150821</v>
       </c>
       <c r="B81" t="n">
-        <v>89391</v>
+        <v>91981</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9138,25 +9138,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>756175</v>
+        <v>756127</v>
       </c>
       <c r="R81" t="n">
-        <v>7458176</v>
+        <v>7458223</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9200,12 +9200,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9237,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121150821</v>
+        <v>121150823</v>
       </c>
       <c r="B82" t="n">
-        <v>91981</v>
+        <v>92015</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9253,21 +9253,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>756127</v>
+        <v>756349</v>
       </c>
       <c r="R82" t="n">
-        <v>7458223</v>
+        <v>7458017</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9311,12 +9311,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9348,10 +9348,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121152431</v>
+        <v>121150825</v>
       </c>
       <c r="B83" t="n">
-        <v>91973</v>
+        <v>89391</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6055</v>
+        <v>6276</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9392,10 +9392,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>756226</v>
+        <v>756175</v>
       </c>
       <c r="R83" t="n">
-        <v>7458150</v>
+        <v>7458176</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9422,12 +9422,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9459,7 +9459,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121150826</v>
+        <v>121150827</v>
       </c>
       <c r="B84" t="n">
         <v>91983</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>756199</v>
+        <v>756515</v>
       </c>
       <c r="R84" t="n">
         <v>7458177</v>
@@ -9570,10 +9570,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121150823</v>
+        <v>121152431</v>
       </c>
       <c r="B85" t="n">
-        <v>92015</v>
+        <v>91973</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9582,25 +9582,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5448</v>
+        <v>6055</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>756349</v>
+        <v>756226</v>
       </c>
       <c r="R85" t="n">
-        <v>7458017</v>
+        <v>7458150</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121152430</v>
+        <v>121150826</v>
       </c>
       <c r="B86" t="n">
-        <v>91973</v>
+        <v>91983</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9693,25 +9693,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>756201</v>
+        <v>756199</v>
       </c>
       <c r="R86" t="n">
-        <v>7458210</v>
+        <v>7458177</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">

--- a/artfynd/A 42147-2024 artfynd.xlsx
+++ b/artfynd/A 42147-2024 artfynd.xlsx
@@ -8793,10 +8793,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121150824</v>
+        <v>121152430</v>
       </c>
       <c r="B78" t="n">
-        <v>91983</v>
+        <v>91973</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8805,30 +8805,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>6055</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>756060</v>
+        <v>756201</v>
       </c>
       <c r="R78" t="n">
-        <v>7458231</v>
+        <v>7458210</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -8904,10 +8904,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121152430</v>
+        <v>121150824</v>
       </c>
       <c r="B79" t="n">
-        <v>91973</v>
+        <v>91983</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8916,30 +8916,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>756201</v>
+        <v>756060</v>
       </c>
       <c r="R79" t="n">
-        <v>7458210</v>
+        <v>7458231</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
